--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_4_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1000000/Output_4_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268900.2608276921</v>
+        <v>273721.3410357452</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4964010.941928675</v>
+        <v>4968231.017992429</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22285259.10284262</v>
+        <v>22289395.19939268</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4042949.682958145</v>
+        <v>4041173.505479912</v>
       </c>
     </row>
     <row r="11">
@@ -2068,25 +2068,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2131,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="21">
@@ -2156,16 +2156,16 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2201,16 +2201,16 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2226,22 +2226,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>9.137025436486057</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="23">
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="I23" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2371,10 +2371,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y23" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2384,22 +2384,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2520,19 +2520,19 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="26">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2599,19 +2599,19 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W26" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X26" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2624,16 +2624,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="F27" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2684,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2763,13 +2763,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="29">
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>23.28271064538745</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -2791,16 +2791,16 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>12.92549025883184</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -2824,16 +2824,16 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2864,16 +2864,16 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2918,16 +2918,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="31">
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C31" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2997,16 +2997,16 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="32">
@@ -3019,28 +3019,28 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>12.92549025883184</v>
       </c>
       <c r="F32" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="33">
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3152,16 +3152,16 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>34.48540867374214</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V33" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W33" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X33" t="n">
-        <v>40</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3186,10 +3186,10 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -3216,25 +3216,25 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>7.256111626157765</v>
       </c>
       <c r="U34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3253,31 +3253,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="E35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>12.92549025883184</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3335,13 +3335,13 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>34.48540867374212</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3350,10 +3350,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>40</v>
+        <v>34.11888750173132</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J36" t="n">
         <v>0.7465913262578567</v>
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="37">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -3453,19 +3453,19 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="T37" t="n">
-        <v>9.137025436486075</v>
+        <v>7.256111626157765</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3502,19 +3502,19 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>12.92549025883184</v>
       </c>
       <c r="I38" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3572,28 +3572,28 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>34.48540867374211</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -3660,22 +3660,22 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -3699,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3742,16 +3742,16 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>12.92549025883184</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3775,22 +3775,22 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>25.24130078545516</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3821,13 +3821,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3860,10 +3860,10 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -3872,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>9.137025436486075</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3930,10 +3930,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3942,16 +3942,16 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="C20" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D20" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E20" t="n">
-        <v>119.5959595959596</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F20" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G20" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="M20" t="n">
-        <v>41.20000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="N20" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O20" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V20" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W20" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="X20" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="Y20" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="C21" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="L21" t="n">
-        <v>3.2</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M21" t="n">
-        <v>42.8</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N21" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O21" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P21" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q21" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R21" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S21" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T21" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U21" t="n">
-        <v>84.00808080808082</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V21" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W21" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>79.19191919191917</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="C22" t="n">
-        <v>38.78787878787876</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="D22" t="n">
-        <v>29.55856016516557</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="E22" t="n">
-        <v>29.55856016516557</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="F22" t="n">
-        <v>29.55856016516557</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G22" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H22" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I22" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J22" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K22" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L22" t="n">
-        <v>56.87268517287855</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M22" t="n">
-        <v>96.06072336510073</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N22" t="n">
-        <v>135.6607233651007</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="U22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="V22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="W22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="X22" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Y22" t="n">
-        <v>119.5959595959596</v>
+        <v>93.21247408113457</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>124.4121212121212</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="C23" t="n">
-        <v>124.4121212121212</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="D23" t="n">
-        <v>124.4121212121212</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="E23" t="n">
-        <v>124.4121212121212</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="F23" t="n">
-        <v>124.4121212121212</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="G23" t="n">
-        <v>84.00808080808082</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="H23" t="n">
-        <v>43.60404040404041</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K23" t="n">
-        <v>42.8</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L23" t="n">
-        <v>82.40000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M23" t="n">
-        <v>120.4</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N23" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O23" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q23" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R23" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S23" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T23" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="U23" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="V23" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="W23" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="X23" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="Y23" t="n">
-        <v>124.4121212121212</v>
+        <v>78.36807964162378</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>84.00808080808082</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="C24" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="D24" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K24" t="n">
-        <v>42.8</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L24" t="n">
-        <v>82.40000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="M24" t="n">
-        <v>120.4</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N24" t="n">
-        <v>120.4</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O24" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P24" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X24" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Y24" t="n">
-        <v>124.4121212121212</v>
+        <v>158.3355078473624</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.55856016516557</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="C25" t="n">
-        <v>29.55856016516557</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="D25" t="n">
-        <v>29.55856016516557</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="E25" t="n">
-        <v>29.55856016516557</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="F25" t="n">
-        <v>29.55856016516557</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G25" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H25" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I25" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J25" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K25" t="n">
-        <v>29.55856016516557</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L25" t="n">
-        <v>56.87268517287855</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M25" t="n">
-        <v>96.06072336510073</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N25" t="n">
-        <v>135.6607233651007</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O25" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P25" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q25" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R25" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S25" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T25" t="n">
-        <v>160</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="U25" t="n">
-        <v>150.7706813772868</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="V25" t="n">
-        <v>110.3666409732464</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="W25" t="n">
-        <v>69.96260056920597</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="X25" t="n">
-        <v>29.55856016516557</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Y25" t="n">
-        <v>29.55856016516557</v>
+        <v>93.21247408113457</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28.69626341965168</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C26" t="n">
-        <v>28.69626341965168</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D26" t="n">
-        <v>28.69626341965168</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E26" t="n">
-        <v>28.69626341965168</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L26" t="n">
-        <v>42.8</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="M26" t="n">
-        <v>42.8</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="N26" t="n">
-        <v>82.40000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O26" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q26" t="n">
-        <v>149.9083846317729</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R26" t="n">
-        <v>149.9083846317729</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S26" t="n">
-        <v>149.9083846317729</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T26" t="n">
-        <v>149.9083846317729</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U26" t="n">
-        <v>149.9083846317729</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="V26" t="n">
-        <v>149.9083846317729</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="W26" t="n">
-        <v>109.5043442277325</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="X26" t="n">
-        <v>69.10030382369209</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y26" t="n">
-        <v>28.69626341965168</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>38.78787878787876</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="C27" t="n">
-        <v>38.78787878787876</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="D27" t="n">
-        <v>38.78787878787876</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="E27" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K27" t="n">
-        <v>42.8</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L27" t="n">
-        <v>82.40000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M27" t="n">
-        <v>82.40000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N27" t="n">
-        <v>82.40000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O27" t="n">
-        <v>82.40000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P27" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q27" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R27" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S27" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T27" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U27" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V27" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W27" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X27" t="n">
-        <v>38.78787878787876</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.78787878787876</v>
+        <v>118.3517937444931</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>133.6414398348344</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C28" t="n">
-        <v>133.6414398348344</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D28" t="n">
-        <v>133.6414398348344</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E28" t="n">
-        <v>93.23739943079403</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F28" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G28" t="n">
-        <v>12.42931862271321</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K28" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L28" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M28" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N28" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="U28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="V28" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="W28" t="n">
-        <v>133.6414398348344</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="X28" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="Y28" t="n">
-        <v>133.6414398348344</v>
+        <v>13.245045875396</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79.19191919191917</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="C29" t="n">
-        <v>55.67402965112376</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="D29" t="n">
-        <v>55.67402965112376</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="E29" t="n">
-        <v>55.67402965112376</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="F29" t="n">
-        <v>55.67402965112376</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="G29" t="n">
-        <v>55.67402965112376</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="H29" t="n">
-        <v>15.26998924708335</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="I29" t="n">
-        <v>15.26998924708335</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K29" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L29" t="n">
-        <v>42.8</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M29" t="n">
-        <v>82.40000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N29" t="n">
-        <v>122</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O29" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P29" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q29" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R29" t="n">
-        <v>119.5959595959596</v>
+        <v>108.260178376266</v>
       </c>
       <c r="S29" t="n">
-        <v>119.5959595959596</v>
+        <v>108.260178376266</v>
       </c>
       <c r="T29" t="n">
-        <v>79.19191919191917</v>
+        <v>108.260178376266</v>
       </c>
       <c r="U29" t="n">
-        <v>79.19191919191917</v>
+        <v>108.260178376266</v>
       </c>
       <c r="V29" t="n">
-        <v>79.19191919191917</v>
+        <v>108.260178376266</v>
       </c>
       <c r="W29" t="n">
-        <v>79.19191919191917</v>
+        <v>108.260178376266</v>
       </c>
       <c r="X29" t="n">
-        <v>79.19191919191917</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="Y29" t="n">
-        <v>79.19191919191917</v>
+        <v>68.2764642733967</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43.60404040404041</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="C30" t="n">
-        <v>43.60404040404041</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="D30" t="n">
-        <v>43.60404040404041</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="E30" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F30" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G30" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K30" t="n">
-        <v>3.2</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L30" t="n">
-        <v>42.8</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="M30" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N30" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O30" t="n">
-        <v>120.4</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="P30" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="Q30" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R30" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S30" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T30" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U30" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V30" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W30" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X30" t="n">
-        <v>43.60404040404041</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="Y30" t="n">
-        <v>43.60404040404041</v>
+        <v>83.13413836268582</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>84.00808080808082</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="C31" t="n">
-        <v>43.60404040404041</v>
+        <v>13.245045875396</v>
       </c>
       <c r="D31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L31" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M31" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="U31" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="V31" t="n">
-        <v>124.4121212121212</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="W31" t="n">
-        <v>84.00808080808082</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="X31" t="n">
-        <v>84.00808080808082</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Y31" t="n">
-        <v>84.00808080808082</v>
+        <v>93.21247408113457</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>69.10030382369209</v>
+        <v>108.260178376266</v>
       </c>
       <c r="C32" t="n">
-        <v>69.10030382369209</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="D32" t="n">
-        <v>69.10030382369209</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="E32" t="n">
-        <v>69.10030382369209</v>
+        <v>55.22041350689989</v>
       </c>
       <c r="F32" t="n">
-        <v>43.60404040404041</v>
+        <v>55.22041350689989</v>
       </c>
       <c r="G32" t="n">
-        <v>43.60404040404041</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="H32" t="n">
-        <v>43.60404040404041</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K32" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L32" t="n">
-        <v>42.8</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M32" t="n">
-        <v>82.40000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N32" t="n">
-        <v>122</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O32" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P32" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q32" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R32" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S32" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T32" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U32" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V32" t="n">
-        <v>109.5043442277325</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W32" t="n">
-        <v>109.5043442277325</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="X32" t="n">
-        <v>109.5043442277325</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="Y32" t="n">
-        <v>69.10030382369209</v>
+        <v>108.260178376266</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K33" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L33" t="n">
-        <v>80.80000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="M33" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N33" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="O33" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P33" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q33" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R33" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S33" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T33" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U33" t="n">
-        <v>125.1662538649069</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="V33" t="n">
-        <v>84.76221346086653</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="W33" t="n">
-        <v>44.35817305682612</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="X33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F34" t="n">
-        <v>12.42931862271321</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G34" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K34" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L34" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M34" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N34" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O34" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P34" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="Q34" t="n">
-        <v>133.6414398348344</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="R34" t="n">
-        <v>133.6414398348344</v>
+        <v>50.47982994280417</v>
       </c>
       <c r="S34" t="n">
-        <v>133.6414398348344</v>
+        <v>10.49611583993489</v>
       </c>
       <c r="T34" t="n">
-        <v>133.6414398348344</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="U34" t="n">
-        <v>93.23739943079403</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="V34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="W34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y34" t="n">
-        <v>52.83335902675362</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84.00808080808082</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="C35" t="n">
-        <v>84.00808080808082</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="D35" t="n">
-        <v>43.60404040404041</v>
+        <v>108.260178376266</v>
       </c>
       <c r="E35" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="G35" t="n">
-        <v>3.2</v>
+        <v>95.20412760976917</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>55.22041350689989</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K35" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L35" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M35" t="n">
-        <v>41.20000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N35" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O35" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P35" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="X35" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="Y35" t="n">
-        <v>119.5959595959596</v>
+        <v>148.2438924791353</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>119.5959595959596</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="C36" t="n">
-        <v>84.76221346086653</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="D36" t="n">
-        <v>84.76221346086653</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="E36" t="n">
-        <v>44.35817305682612</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="F36" t="n">
-        <v>44.35817305682612</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="G36" t="n">
-        <v>44.35817305682612</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="H36" t="n">
-        <v>3.954132652785714</v>
+        <v>43.90455691260225</v>
       </c>
       <c r="I36" t="n">
-        <v>3.954132652785714</v>
+        <v>3.920842809732961</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K36" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L36" t="n">
-        <v>42.8</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="M36" t="n">
-        <v>82.40000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="N36" t="n">
-        <v>122</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="O36" t="n">
-        <v>160</v>
+        <v>81.54278654139161</v>
       </c>
       <c r="P36" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R36" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S36" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T36" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U36" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V36" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="W36" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="X36" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="Y36" t="n">
-        <v>119.5959595959596</v>
+        <v>78.36807964162378</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="C37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L37" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M37" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N37" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O37" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P37" t="n">
-        <v>133.6414398348344</v>
+        <v>130.4472581485427</v>
       </c>
       <c r="Q37" t="n">
-        <v>133.6414398348344</v>
+        <v>90.46354404567346</v>
       </c>
       <c r="R37" t="n">
-        <v>133.6414398348344</v>
+        <v>50.47982994280417</v>
       </c>
       <c r="S37" t="n">
-        <v>133.6414398348344</v>
+        <v>10.49611583993489</v>
       </c>
       <c r="T37" t="n">
-        <v>124.4121212121212</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="U37" t="n">
-        <v>124.4121212121212</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="V37" t="n">
-        <v>124.4121212121212</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="W37" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="X37" t="n">
-        <v>84.00808080808082</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="Y37" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="C38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="D38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="E38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="F38" t="n">
-        <v>43.60404040404041</v>
+        <v>108.260178376266</v>
       </c>
       <c r="G38" t="n">
-        <v>43.60404040404041</v>
+        <v>68.2764642733967</v>
       </c>
       <c r="H38" t="n">
-        <v>43.60404040404041</v>
+        <v>55.22041350689989</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K38" t="n">
-        <v>42.8</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L38" t="n">
-        <v>80.80000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M38" t="n">
-        <v>80.80000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N38" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O38" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P38" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q38" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R38" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S38" t="n">
-        <v>109.5043442277325</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T38" t="n">
-        <v>69.10030382369209</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U38" t="n">
-        <v>69.10030382369209</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="X38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="Y38" t="n">
-        <v>43.60404040404041</v>
+        <v>148.2438924791353</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="C39" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D39" t="n">
-        <v>160</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E39" t="n">
-        <v>119.5959595959596</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F39" t="n">
-        <v>79.19191919191917</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G39" t="n">
-        <v>44.35817305682612</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H39" t="n">
-        <v>44.35817305682612</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I39" t="n">
-        <v>3.954132652785714</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K39" t="n">
-        <v>3.2</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="L39" t="n">
-        <v>41.20000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="M39" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N39" t="n">
-        <v>120.4</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O39" t="n">
-        <v>160</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="P39" t="n">
-        <v>160</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="Q39" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R39" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="S39" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="T39" t="n">
-        <v>160</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="U39" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="V39" t="n">
-        <v>160</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="W39" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="X39" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="Y39" t="n">
-        <v>160</v>
+        <v>38.38436553875449</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>52.83335902675362</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="C40" t="n">
-        <v>52.83335902675362</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="D40" t="n">
-        <v>52.83335902675362</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="E40" t="n">
-        <v>52.83335902675362</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="F40" t="n">
-        <v>12.42931862271321</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="G40" t="n">
-        <v>3.2</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>13.245045875396</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>13.245045875396</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L40" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M40" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N40" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O40" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P40" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q40" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R40" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S40" t="n">
-        <v>93.23739943079403</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T40" t="n">
-        <v>93.23739943079403</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="U40" t="n">
-        <v>93.23739943079403</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="V40" t="n">
-        <v>93.23739943079403</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="W40" t="n">
-        <v>93.23739943079403</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="X40" t="n">
-        <v>93.23739943079403</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="Y40" t="n">
-        <v>52.83335902675362</v>
+        <v>93.21247408113457</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="C41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="D41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="E41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="F41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="G41" t="n">
-        <v>3.2</v>
+        <v>95.20412760976917</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>55.22041350689989</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>15.2366994040306</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M41" t="n">
-        <v>42.8</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N41" t="n">
-        <v>82.40000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O41" t="n">
-        <v>122</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q41" t="n">
-        <v>149.9083846317729</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R41" t="n">
-        <v>109.5043442277325</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S41" t="n">
-        <v>109.5043442277325</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T41" t="n">
-        <v>69.10030382369209</v>
+        <v>108.260178376266</v>
       </c>
       <c r="U41" t="n">
-        <v>69.10030382369209</v>
+        <v>108.260178376266</v>
       </c>
       <c r="V41" t="n">
-        <v>28.69626341965168</v>
+        <v>108.260178376266</v>
       </c>
       <c r="W41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="X41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.2</v>
+        <v>108.260178376266</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="C42" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="D42" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="E42" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="F42" t="n">
-        <v>3.2</v>
+        <v>123.1178524655551</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>83.13413836268582</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K42" t="n">
-        <v>3.2</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L42" t="n">
-        <v>3.2</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="N42" t="n">
-        <v>41.20000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O42" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="P42" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T42" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="U42" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="V42" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="W42" t="n">
-        <v>79.19191919191917</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="X42" t="n">
-        <v>43.60404040404041</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.2</v>
+        <v>158.3355078473624</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52.83335902675362</v>
+        <v>13.245045875396</v>
       </c>
       <c r="C43" t="n">
-        <v>52.83335902675362</v>
+        <v>13.245045875396</v>
       </c>
       <c r="D43" t="n">
-        <v>52.83335902675362</v>
+        <v>13.245045875396</v>
       </c>
       <c r="E43" t="n">
-        <v>52.83335902675362</v>
+        <v>13.245045875396</v>
       </c>
       <c r="F43" t="n">
-        <v>52.83335902675362</v>
+        <v>13.245045875396</v>
       </c>
       <c r="G43" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H43" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I43" t="n">
-        <v>43.60404040404041</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L43" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M43" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N43" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q43" t="n">
-        <v>133.6414398348344</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="R43" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="S43" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="T43" t="n">
-        <v>133.6414398348344</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="U43" t="n">
-        <v>133.6414398348344</v>
+        <v>13.245045875396</v>
       </c>
       <c r="V43" t="n">
-        <v>133.6414398348344</v>
+        <v>13.245045875396</v>
       </c>
       <c r="W43" t="n">
-        <v>93.23739943079403</v>
+        <v>13.245045875396</v>
       </c>
       <c r="X43" t="n">
-        <v>52.83335902675362</v>
+        <v>13.245045875396</v>
       </c>
       <c r="Y43" t="n">
-        <v>52.83335902675362</v>
+        <v>13.245045875396</v>
       </c>
     </row>
     <row r="44">
@@ -9381,22 +9381,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>220.0898510449805</v>
+        <v>258.0743794427063</v>
       </c>
       <c r="L20" t="n">
-        <v>235.7664149699872</v>
+        <v>275.3502919318278</v>
       </c>
       <c r="M20" t="n">
-        <v>268.7300716111112</v>
+        <v>269.9301101891133</v>
       </c>
       <c r="N20" t="n">
-        <v>269.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>270.0982114216868</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P20" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>175.8259673720848</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>182.1340339220183</v>
+        <v>181.7179108838589</v>
       </c>
       <c r="N21" t="n">
-        <v>169.7255504671717</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O21" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q21" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9548,7 +9548,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N22" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O22" t="n">
         <v>163.0416663658825</v>
@@ -9618,22 +9618,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L23" t="n">
-        <v>275.7664149699872</v>
+        <v>275.3502919318278</v>
       </c>
       <c r="M23" t="n">
-        <v>268.7300716111111</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O23" t="n">
-        <v>230.0982114216867</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P23" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>177.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L24" t="n">
-        <v>178.5543797798742</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M24" t="n">
-        <v>180.5178723058567</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444444</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q24" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9785,7 +9785,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N25" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O25" t="n">
         <v>163.0416663658825</v>
@@ -9855,22 +9855,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>220.0898510449805</v>
+        <v>259.6737280068211</v>
       </c>
       <c r="L26" t="n">
-        <v>275.7664149699872</v>
+        <v>275.3502919318278</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N26" t="n">
-        <v>269.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>268.4820498055251</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P26" t="n">
-        <v>271.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>177.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>178.5543797798742</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>180.1185623197441</v>
       </c>
       <c r="N27" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P27" t="n">
-        <v>172.3582457981686</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q27" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10022,7 +10022,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N28" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O28" t="n">
         <v>163.0416663658825</v>
@@ -10095,19 +10095,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L29" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
-        <v>270.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N29" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O29" t="n">
-        <v>268.4820498055251</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P29" t="n">
-        <v>231.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L30" t="n">
-        <v>178.5543797798742</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M30" t="n">
-        <v>180.5178723058567</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>173.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>179.5656510478621</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10259,7 +10259,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N31" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O31" t="n">
         <v>163.0416663658825</v>
@@ -10332,19 +10332,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>275.7664149699872</v>
+        <v>273.750943367713</v>
       </c>
       <c r="M32" t="n">
-        <v>270.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N32" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O32" t="n">
-        <v>268.4820498055251</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>176.2252773581974</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>178.5543797798742</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>181.7179108838589</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O33" t="n">
-        <v>182.5962444444444</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10496,7 +10496,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N34" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O34" t="n">
         <v>163.0416663658825</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>258.4736894288189</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N35" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O35" t="n">
-        <v>270.0982114216868</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P35" t="n">
-        <v>271.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>178.5543797798742</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M36" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>180.9800828282828</v>
+        <v>182.180121406285</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>171.9589358120561</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>179.5656510478621</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10733,7 +10733,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N37" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O37" t="n">
         <v>163.0416663658825</v>
@@ -10803,22 +10803,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L38" t="n">
-        <v>274.1502533538256</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M38" t="n">
-        <v>230.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N38" t="n">
-        <v>229.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O38" t="n">
-        <v>270.0982114216868</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P38" t="n">
-        <v>271.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>175.8259673720848</v>
       </c>
       <c r="L39" t="n">
-        <v>176.9382181637126</v>
+        <v>178.1382567417148</v>
       </c>
       <c r="M39" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>171.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>179.5656510478621</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10970,7 +10970,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N40" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O40" t="n">
         <v>163.0416663658825</v>
@@ -11046,16 +11046,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>270.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N41" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O41" t="n">
-        <v>270.0982114216868</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P41" t="n">
-        <v>269.6168341391079</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M42" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>173.9744074143302</v>
+        <v>173.5582843761708</v>
       </c>
       <c r="Q42" t="n">
-        <v>179.9817740860215</v>
+        <v>179.5656510478621</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11207,7 +11207,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N43" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O43" t="n">
         <v>163.0416663658825</v>
@@ -23926,25 +23926,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>343.14996470164</v>
       </c>
       <c r="C20" t="n">
-        <v>365.2728917710076</v>
+        <v>330.4074129430184</v>
       </c>
       <c r="D20" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>304.2428021157672</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
@@ -23989,13 +23989,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>309.6570917555724</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="21">
@@ -24014,16 +24014,16 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>157.6450804554009</v>
+        <v>122.7796016274118</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>105.4853354315433</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>97.75964020137005</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>72.65156727465587</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -24059,16 +24059,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>160.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>190.7093820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
@@ -24084,22 +24084,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>139.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
-        <v>139.4784475817263</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E22" t="n">
-        <v>146.4339626465692</v>
+        <v>136.4564102853049</v>
       </c>
       <c r="F22" t="n">
-        <v>145.4210480229312</v>
+        <v>105.8371710610907</v>
       </c>
       <c r="G22" t="n">
-        <v>167.9909793584588</v>
+        <v>128.4071023966182</v>
       </c>
       <c r="H22" t="n">
         <v>162.2271725074396</v>
@@ -24153,7 +24153,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
-        <v>178.5846533520948</v>
+        <v>179.0007763902542</v>
       </c>
     </row>
     <row r="23">
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>375.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>299.4748021157671</v>
+        <v>304.609323287778</v>
       </c>
       <c r="I23" t="n">
-        <v>170.4758895704059</v>
+        <v>170.8920126085653</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24217,7 +24217,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>183.5119726022908</v>
       </c>
       <c r="U23" t="n">
         <v>251.3456529078365</v>
@@ -24229,10 +24229,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>330.1472237166284</v>
       </c>
       <c r="Y23" t="n">
-        <v>351.0059386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24242,22 +24242,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>126.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>107.4450655646388</v>
+        <v>112.5795867366496</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>118.0612034935604</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>105.4853354315433</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>97.75964020137005</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24311,7 +24311,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>170.4506957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>179.8319801819373</v>
+        <v>140.2481032200967</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24333,10 +24333,10 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F25" t="n">
-        <v>145.4210480229312</v>
+        <v>135.443495661667</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>128.4071023966182</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24378,19 +24378,19 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>277.1820039200048</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
-        <v>212.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X25" t="n">
-        <v>185.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
-        <v>218.5846533520948</v>
+        <v>179.0007763902542</v>
       </c>
     </row>
     <row r="26">
@@ -24412,7 +24412,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>381.6347449562563</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
         <v>415.302737515135</v>
@@ -24445,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
         <v>149.8691179411497</v>
@@ -24457,19 +24457,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>211.7617759459959</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>288.1683815082943</v>
       </c>
       <c r="W26" t="n">
-        <v>309.240968717413</v>
+        <v>309.6570917555724</v>
       </c>
       <c r="X26" t="n">
-        <v>329.731100678469</v>
+        <v>334.8656218504798</v>
       </c>
       <c r="Y26" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24482,16 +24482,16 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>133.1246220264752</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>107.8611886027982</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>122.7796016274118</v>
       </c>
       <c r="F27" t="n">
-        <v>109.8372123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
         <v>137.3435171632106</v>
@@ -24527,7 +24527,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>60.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
@@ -24542,10 +24542,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>165.7729852034775</v>
+        <v>166.1891082416369</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>179.8319801819373</v>
+        <v>169.854427820673</v>
       </c>
       <c r="C28" t="n">
         <v>167.2468210986278</v>
@@ -24567,16 +24567,16 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E28" t="n">
-        <v>106.4339626465692</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F28" t="n">
-        <v>105.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>127.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H28" t="n">
-        <v>153.0901470709535</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I28" t="n">
         <v>155.4504749272583</v>
@@ -24621,13 +24621,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>286.522998336591</v>
+        <v>246.9391213747504</v>
       </c>
       <c r="X28" t="n">
-        <v>225.7096553890372</v>
+        <v>186.1257784271966</v>
       </c>
       <c r="Y28" t="n">
-        <v>218.5846533520948</v>
+        <v>179.0007763902542</v>
       </c>
     </row>
     <row r="29">
@@ -24640,7 +24640,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>341.9901811256201</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
@@ -24649,16 +24649,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>367.2921687798708</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>299.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
-        <v>210.4758895704059</v>
+        <v>197.5503993115741</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24682,16 +24682,16 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>109.8691179411497</v>
+        <v>110.2852409793091</v>
       </c>
       <c r="S29" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
         <v>251.3456529078365</v>
@@ -24703,7 +24703,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>330.1472237166284</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24722,16 +24722,16 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>107.8611886027982</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>118.0612034935604</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>97.34351716321063</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>60.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -24776,16 +24776,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>192.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>216.4629831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>170.9075063754883</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>166.0988188154638</v>
       </c>
     </row>
     <row r="31">
@@ -24795,13 +24795,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>179.8319801819373</v>
+        <v>140.2481032200967</v>
       </c>
       <c r="C31" t="n">
-        <v>127.2468210986278</v>
+        <v>127.6629441367872</v>
       </c>
       <c r="D31" t="n">
-        <v>148.6154730182124</v>
+        <v>138.6379206569481</v>
       </c>
       <c r="E31" t="n">
         <v>146.4339626465692</v>
@@ -24816,7 +24816,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -24855,16 +24855,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V31" t="n">
-        <v>243.0006178873419</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X31" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>179.0007763902542</v>
       </c>
     </row>
     <row r="32">
@@ -24877,28 +24877,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>325.689014809167</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>369.00487981343</v>
       </c>
       <c r="F32" t="n">
-        <v>381.6347449562563</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>375.7188605532945</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>170.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24934,7 +24934,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
@@ -24943,7 +24943,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>346.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="33">
@@ -24977,7 +24977,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25010,16 +25010,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>191.4559734072327</v>
+        <v>186.3575051191342</v>
       </c>
       <c r="V33" t="n">
-        <v>192.8005871494253</v>
+        <v>193.2167101875847</v>
       </c>
       <c r="W33" t="n">
-        <v>211.6949831609196</v>
+        <v>212.111106199079</v>
       </c>
       <c r="X33" t="n">
-        <v>165.7729852034775</v>
+        <v>170.9075063754883</v>
       </c>
       <c r="Y33" t="n">
         <v>205.6826957773044</v>
@@ -25044,10 +25044,10 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>105.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>158.8539539219727</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H34" t="n">
         <v>162.2271725074396</v>
@@ -25074,25 +25074,25 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>86.16204325169439</v>
+        <v>46.5781662898538</v>
       </c>
       <c r="R34" t="n">
-        <v>177.2933913771695</v>
+        <v>137.7095144153289</v>
       </c>
       <c r="S34" t="n">
-        <v>224.0165980369723</v>
+        <v>184.4327210751317</v>
       </c>
       <c r="T34" t="n">
-        <v>227.9455894282815</v>
+        <v>220.6894778021237</v>
       </c>
       <c r="U34" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
-        <v>212.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
         <v>286.522998336591</v>
@@ -25111,31 +25111,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>347.5018416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>314.683041620683</v>
+        <v>315.0991646588424</v>
       </c>
       <c r="E35" t="n">
-        <v>341.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>415.302737515135</v>
+        <v>402.3772472563032</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>299.8909251539266</v>
       </c>
       <c r="I35" t="n">
-        <v>210.4758895704059</v>
+        <v>170.8920126085653</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25180,7 +25180,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25193,13 +25193,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>138.2230903145736</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>117.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
@@ -25208,10 +25208,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>72.23544423649646</v>
+        <v>78.11655673476514</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>49.81275588957449</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,7 +25238,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>60.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
         <v>171.6831711038378</v>
@@ -25250,7 +25250,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>193.2167101875847</v>
       </c>
       <c r="W36" t="n">
         <v>251.6949831609196</v>
@@ -25259,7 +25259,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>166.0988188154638</v>
       </c>
     </row>
     <row r="37">
@@ -25269,7 +25269,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>139.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C37" t="n">
         <v>167.2468210986278</v>
@@ -25311,19 +25311,19 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>86.16204325169439</v>
+        <v>46.5781662898538</v>
       </c>
       <c r="R37" t="n">
-        <v>177.2933913771695</v>
+        <v>137.7095144153289</v>
       </c>
       <c r="S37" t="n">
-        <v>224.0165980369723</v>
+        <v>184.4327210751317</v>
       </c>
       <c r="T37" t="n">
-        <v>218.8085639917954</v>
+        <v>220.6894778021237</v>
       </c>
       <c r="U37" t="n">
         <v>286.3190293564909</v>
@@ -25332,13 +25332,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y37" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="38">
@@ -25360,19 +25360,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>406.8760457417114</v>
+        <v>367.2921687798708</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>375.7188605532945</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>326.5493118569353</v>
       </c>
       <c r="I38" t="n">
-        <v>170.4758895704059</v>
+        <v>170.8920126085653</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25399,16 +25399,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>169.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>302.5109576846797</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
@@ -25430,28 +25430,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>137.8430201603266</v>
       </c>
       <c r="D39" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>117.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>105.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>102.8581084894685</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>49.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>60.57395719080255</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
@@ -25484,13 +25484,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>186.3575051191342</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>212.111106199079</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
@@ -25509,7 +25509,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C40" t="n">
-        <v>167.2468210986278</v>
+        <v>127.6629441367872</v>
       </c>
       <c r="D40" t="n">
         <v>148.6154730182124</v>
@@ -25518,22 +25518,22 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F40" t="n">
-        <v>105.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>158.8539539219727</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H40" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I40" t="n">
-        <v>155.4504749272583</v>
+        <v>115.8665979654177</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K40" t="n">
-        <v>22.26949182588285</v>
+        <v>12.29193946461858</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -25557,10 +25557,10 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>227.9455894282815</v>
+        <v>188.3617124664409</v>
       </c>
       <c r="U40" t="n">
         <v>286.3190293564909</v>
@@ -25575,7 +25575,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y40" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="41">
@@ -25600,16 +25600,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>402.3772472563032</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>299.8909251539266</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>170.8920126085653</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25633,22 +25633,22 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>109.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>183.0958495641314</v>
+        <v>183.5119726022908</v>
       </c>
       <c r="U41" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>323.9996679319578</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
@@ -25670,7 +25670,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>112.5795867366496</v>
       </c>
       <c r="E42" t="n">
         <v>157.6450804554009</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>97.75964020137005</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>72.65156727465587</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>49.81275588957449</v>
       </c>
       <c r="J42" t="n">
         <v>0.7465913262578567</v>
@@ -25718,10 +25718,10 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>160.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25730,10 +25730,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
-        <v>170.5409852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -25758,7 +25758,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>158.8539539219727</v>
+        <v>158.0134269971945</v>
       </c>
       <c r="H43" t="n">
         <v>162.2271725074396</v>
@@ -25767,7 +25767,7 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J43" t="n">
-        <v>53.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K43" t="n">
         <v>22.26949182588285</v>
@@ -25788,10 +25788,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>86.16204325169439</v>
+        <v>46.5781662898538</v>
       </c>
       <c r="R43" t="n">
-        <v>177.2933913771695</v>
+        <v>137.7095144153289</v>
       </c>
       <c r="S43" t="n">
         <v>224.0165980369723</v>
@@ -25800,16 +25800,16 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3190293564909</v>
+        <v>246.7351523946503</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
-        <v>185.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
         <v>218.5846533520948</v>
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367475.9709332837</v>
+        <v>367155.0035530833</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367475.9709332836</v>
+        <v>367155.0035530833</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367475.9709332836</v>
+        <v>367155.0035530833</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367475.9709332837</v>
+        <v>367155.0035530833</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367475.9709332836</v>
+        <v>367155.0035530834</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367475.9709332837</v>
+        <v>367155.0035530832</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367475.9709332836</v>
+        <v>367155.0035530834</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367475.9709332836</v>
+        <v>367155.0035530834</v>
       </c>
     </row>
     <row r="16">
@@ -26261,7 +26261,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64504.44331886783</v>
+        <v>64504.44331886782</v>
       </c>
       <c r="C2" t="n">
         <v>64504.44331886783</v>
@@ -26270,37 +26270,37 @@
         <v>64504.44331886783</v>
       </c>
       <c r="E2" t="n">
+        <v>64504.44331886783</v>
+      </c>
+      <c r="F2" t="n">
         <v>64504.44331886784</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>64504.44331886783</v>
       </c>
-      <c r="G2" t="n">
-        <v>64504.44331886782</v>
-      </c>
       <c r="H2" t="n">
-        <v>71115.72110201053</v>
+        <v>71053.6796537592</v>
       </c>
       <c r="I2" t="n">
-        <v>71115.72110201053</v>
+        <v>71053.6796537592</v>
       </c>
       <c r="J2" t="n">
-        <v>71115.72110201052</v>
+        <v>71053.67965375919</v>
       </c>
       <c r="K2" t="n">
-        <v>71115.72110201055</v>
+        <v>71053.67965375917</v>
       </c>
       <c r="L2" t="n">
-        <v>71115.72110201053</v>
+        <v>71053.67965375919</v>
       </c>
       <c r="M2" t="n">
-        <v>71115.72110201052</v>
+        <v>71053.67965375914</v>
       </c>
       <c r="N2" t="n">
-        <v>71115.72110201052</v>
+        <v>71053.67965375917</v>
       </c>
       <c r="O2" t="n">
-        <v>71115.72110201052</v>
+        <v>71053.67965375917</v>
       </c>
       <c r="P2" t="n">
         <v>64504.44331886782</v>
@@ -26331,7 +26331,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10792.36</v>
+        <v>10680.08625919725</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
       <c r="C4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
       <c r="D4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
       <c r="E4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
       <c r="F4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
       <c r="G4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
       <c r="H4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="I4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="J4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="K4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="L4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="M4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="N4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="O4" t="n">
-        <v>23783.71317440812</v>
+        <v>23151.83943273248</v>
       </c>
       <c r="P4" t="n">
-        <v>21501.48110628928</v>
+        <v>20948.32715815079</v>
       </c>
     </row>
     <row r="5">
@@ -26435,28 +26435,28 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="I5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="J5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="K5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="L5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="M5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="N5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="O5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9375.362212578555</v>
+        <v>9928.51616071703</v>
       </c>
       <c r="C6" t="n">
-        <v>9375.362212578555</v>
+        <v>9928.516160717038</v>
       </c>
       <c r="D6" t="n">
-        <v>9375.362212578555</v>
+        <v>9928.516160717038</v>
       </c>
       <c r="E6" t="n">
-        <v>43002.96221257857</v>
+        <v>43556.11616071704</v>
       </c>
       <c r="F6" t="n">
-        <v>43002.96221257855</v>
+        <v>43556.11616071704</v>
       </c>
       <c r="G6" t="n">
-        <v>43002.96221257854</v>
+        <v>43556.11616071704</v>
       </c>
       <c r="H6" t="n">
-        <v>34107.6479276024</v>
+        <v>34815.05424254957</v>
       </c>
       <c r="I6" t="n">
-        <v>44900.00792760241</v>
+        <v>45495.14050174681</v>
       </c>
       <c r="J6" t="n">
-        <v>44900.00792760239</v>
+        <v>45495.1405017468</v>
       </c>
       <c r="K6" t="n">
-        <v>44900.00792760243</v>
+        <v>45495.14050174678</v>
       </c>
       <c r="L6" t="n">
-        <v>44900.00792760241</v>
+        <v>45495.1405017468</v>
       </c>
       <c r="M6" t="n">
-        <v>44900.0079276024</v>
+        <v>45495.14050174676</v>
       </c>
       <c r="N6" t="n">
-        <v>44900.00792760239</v>
+        <v>45495.14050174678</v>
       </c>
       <c r="O6" t="n">
-        <v>44900.00792760239</v>
+        <v>45495.14050174678</v>
       </c>
       <c r="P6" t="n">
-        <v>43002.96221257854</v>
+        <v>43556.11616071703</v>
       </c>
     </row>
   </sheetData>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26931,10 +26931,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
   </sheetData>
@@ -36036,22 +36036,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M20" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N21" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36203,7 +36203,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O22" t="n">
         <v>24.58512791403967</v>
@@ -36273,22 +36273,22 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M23" t="n">
-        <v>38.38383838383839</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L24" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M24" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36440,7 +36440,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O25" t="n">
         <v>24.58512791403967</v>
@@ -36510,22 +36510,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P27" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36677,7 +36677,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O28" t="n">
         <v>24.58512791403967</v>
@@ -36750,19 +36750,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O29" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M30" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36914,7 +36914,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O31" t="n">
         <v>24.58512791403967</v>
@@ -36987,19 +36987,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O32" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O33" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37151,7 +37151,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O34" t="n">
         <v>24.58512791403967</v>
@@ -37221,22 +37221,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N35" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37388,7 +37388,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O37" t="n">
         <v>24.58512791403967</v>
@@ -37458,22 +37458,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O38" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P38" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="L39" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="M39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37625,7 +37625,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O40" t="n">
         <v>24.58512791403967</v>
@@ -37701,16 +37701,16 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P41" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O43" t="n">
         <v>24.58512791403967</v>
